--- a/branches/ci/gh-pages-preview/CodeSystem-mii-cs-kardio-supplement-snomedct.xlsx
+++ b/branches/ci/gh-pages-preview/CodeSystem-mii-cs-kardio-supplement-snomedct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -117,7 +117,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20250701</t>
+    <t>http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260701</t>
   </si>
   <si>
     <t>Count</t>
@@ -144,16 +144,16 @@
     <t>368009|Heart valve disorder|:{116676008|Associated morphology|=49755003|Morphologically abnormal structure|,363698007|Finding site|=17401000|Cardiac valve structure|},{246112005|Severity|=24484000|Severe|}</t>
   </si>
   <si>
-    <t>73544002:{260507000=260519008}</t>
-  </si>
-  <si>
-    <t>73544002|Operation on heart valve|:{260507000|Access|=260519008|Transcatheter approach|}</t>
-  </si>
-  <si>
-    <t>64572001:{116676008=50960005,47429007=131148009,42752001=789750003,246112005=24484000}</t>
-  </si>
-  <si>
-    <t>64572001|Disease|:{116676008|Associated morphology|=50960005|Hemorrhage|,47429007|Associated with|=131148009|Bleeding|,42752001|Due to|=789750003|Spontaneous event|,246112005|Severity|=24484000|Severe|}</t>
+    <t>73544002:{260507000=103388001}</t>
+  </si>
+  <si>
+    <t>73544002|Operation on heart valve|:{260507000|Access|=103388001|Percutaneous approach - access|}</t>
+  </si>
+  <si>
+    <t>131148009:{42752001=789750003,246112005=24484000}</t>
+  </si>
+  <si>
+    <t>131148009|Bleeding|:{42752001|Due to|=789750003|Spontaneous event|,246112005|Severity|=24484000|Severe|}</t>
   </si>
 </sst>
 </file>
